--- a/docs/source data 3.xlsx
+++ b/docs/source data 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\Desktop\network-packet-classification\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lab\Desktop\network-packet-classification\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A6A31D-76B4-4AC7-9455-B70B81D1796D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F8CBD0-D744-4871-B950-F3FB0BA00096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tmp" sheetId="7" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="72">
   <si>
     <t>1us: ^(-3) ms</t>
   </si>
@@ -28254,9 +28254,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -28294,7 +28294,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -28400,7 +28400,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -28542,7 +28542,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -28551,26 +28551,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4304A094-1436-4F45-90CB-0949A006A306}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="9" width="12.796875" customWidth="1"/>
+    <col min="1" max="9" width="12.77734375" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="17" width="12.796875" customWidth="1"/>
-    <col min="18" max="18" width="11.296875" customWidth="1"/>
-    <col min="19" max="19" width="10.8984375" customWidth="1"/>
-    <col min="20" max="20" width="9.3984375" customWidth="1"/>
-    <col min="21" max="22" width="12.796875" customWidth="1"/>
-    <col min="23" max="23" width="14.19921875" customWidth="1"/>
+    <col min="12" max="17" width="12.77734375" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" customWidth="1"/>
+    <col min="20" max="20" width="9.44140625" customWidth="1"/>
+    <col min="21" max="22" width="12.77734375" customWidth="1"/>
+    <col min="23" max="23" width="14.21875" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="25" width="20.5" customWidth="1"/>
-    <col min="26" max="26" width="18.59765625" customWidth="1"/>
-    <col min="27" max="27" width="19.8984375" customWidth="1"/>
-    <col min="28" max="28" width="27.69921875" customWidth="1"/>
-    <col min="29" max="29" width="42.296875" customWidth="1"/>
-    <col min="30" max="30" width="36.09765625" customWidth="1"/>
-    <col min="31" max="31" width="11.8984375" customWidth="1"/>
-    <col min="32" max="32" width="8.796875" customWidth="1"/>
+    <col min="25" max="25" width="20.44140625" customWidth="1"/>
+    <col min="26" max="26" width="18.5546875" customWidth="1"/>
+    <col min="27" max="27" width="19.88671875" customWidth="1"/>
+    <col min="28" max="28" width="27.6640625" customWidth="1"/>
+    <col min="29" max="29" width="42.33203125" customWidth="1"/>
+    <col min="30" max="30" width="36.109375" customWidth="1"/>
+    <col min="31" max="31" width="11.88671875" customWidth="1"/>
+    <col min="32" max="32" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -32628,26 +32628,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1818D2-3FAD-40A7-AD2E-4D4E0AB600A3}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="9" width="12.796875" customWidth="1"/>
+    <col min="1" max="9" width="12.77734375" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="17" width="12.796875" customWidth="1"/>
-    <col min="18" max="18" width="11.296875" customWidth="1"/>
-    <col min="19" max="19" width="10.8984375" customWidth="1"/>
-    <col min="20" max="20" width="9.3984375" customWidth="1"/>
-    <col min="21" max="22" width="12.796875" customWidth="1"/>
-    <col min="23" max="23" width="14.19921875" customWidth="1"/>
+    <col min="12" max="17" width="12.77734375" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" customWidth="1"/>
+    <col min="20" max="20" width="9.44140625" customWidth="1"/>
+    <col min="21" max="22" width="12.77734375" customWidth="1"/>
+    <col min="23" max="23" width="14.21875" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="25" width="20.5" customWidth="1"/>
-    <col min="26" max="26" width="18.59765625" customWidth="1"/>
-    <col min="27" max="27" width="19.8984375" customWidth="1"/>
-    <col min="28" max="28" width="27.69921875" customWidth="1"/>
-    <col min="29" max="29" width="42.296875" customWidth="1"/>
-    <col min="30" max="30" width="36.09765625" customWidth="1"/>
-    <col min="31" max="31" width="11.8984375" customWidth="1"/>
-    <col min="32" max="32" width="8.796875" customWidth="1"/>
+    <col min="25" max="25" width="20.44140625" customWidth="1"/>
+    <col min="26" max="26" width="18.5546875" customWidth="1"/>
+    <col min="27" max="27" width="19.88671875" customWidth="1"/>
+    <col min="28" max="28" width="27.6640625" customWidth="1"/>
+    <col min="29" max="29" width="42.33203125" customWidth="1"/>
+    <col min="30" max="30" width="36.109375" customWidth="1"/>
+    <col min="31" max="31" width="11.88671875" customWidth="1"/>
+    <col min="32" max="32" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -36705,22 +36705,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD57"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="9" width="12.796875" customWidth="1"/>
-    <col min="10" max="10" width="16.09765625" customWidth="1"/>
+    <col min="1" max="9" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="17" width="12.796875" customWidth="1"/>
+    <col min="12" max="17" width="12.77734375" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="22" width="12.796875" customWidth="1"/>
-    <col min="23" max="23" width="14.19921875" customWidth="1"/>
+    <col min="19" max="22" width="12.77734375" customWidth="1"/>
+    <col min="23" max="23" width="14.21875" customWidth="1"/>
     <col min="24" max="24" width="21" customWidth="1"/>
-    <col min="25" max="25" width="20.5" customWidth="1"/>
-    <col min="26" max="26" width="18.59765625" customWidth="1"/>
-    <col min="27" max="27" width="19.8984375" customWidth="1"/>
-    <col min="28" max="28" width="27.69921875" customWidth="1"/>
-    <col min="29" max="29" width="42.296875" customWidth="1"/>
-    <col min="30" max="30" width="36.09765625" customWidth="1"/>
+    <col min="25" max="25" width="20.44140625" customWidth="1"/>
+    <col min="26" max="26" width="18.5546875" customWidth="1"/>
+    <col min="27" max="27" width="19.88671875" customWidth="1"/>
+    <col min="28" max="28" width="27.6640625" customWidth="1"/>
+    <col min="29" max="29" width="42.33203125" customWidth="1"/>
+    <col min="30" max="30" width="36.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -40776,43 +40776,43 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AN57"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="A1:AO57"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="10" width="12.796875" customWidth="1"/>
-    <col min="11" max="11" width="10.296875" customWidth="1"/>
-    <col min="12" max="12" width="12.796875" customWidth="1"/>
+    <col min="1" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10.796875" customWidth="1"/>
-    <col min="15" max="15" width="12.796875" customWidth="1"/>
-    <col min="16" max="16" width="11.09765625" customWidth="1"/>
-    <col min="17" max="17" width="12.796875" customWidth="1"/>
-    <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="44" customWidth="1"/>
-    <col min="20" max="20" width="35.796875" customWidth="1"/>
-    <col min="21" max="21" width="36.19921875" customWidth="1"/>
-    <col min="22" max="22" width="5.8984375" customWidth="1"/>
-    <col min="23" max="23" width="15.296875" customWidth="1"/>
-    <col min="24" max="24" width="14.8984375" customWidth="1"/>
-    <col min="25" max="25" width="14.5" customWidth="1"/>
-    <col min="26" max="26" width="15.19921875" customWidth="1"/>
-    <col min="27" max="27" width="15.8984375" customWidth="1"/>
-    <col min="28" max="28" width="9.8984375" customWidth="1"/>
-    <col min="29" max="29" width="9.69921875" customWidth="1"/>
-    <col min="30" max="30" width="8.796875" customWidth="1"/>
-    <col min="31" max="32" width="17" customWidth="1"/>
-    <col min="33" max="33" width="17.5" customWidth="1"/>
-    <col min="34" max="34" width="18.59765625" customWidth="1"/>
-    <col min="35" max="35" width="16.09765625" customWidth="1"/>
-    <col min="37" max="37" width="13.69921875" customWidth="1"/>
-    <col min="38" max="38" width="56.19921875" customWidth="1"/>
-    <col min="39" max="39" width="44.5" customWidth="1"/>
-    <col min="40" max="40" width="43.5" customWidth="1"/>
-    <col min="41" max="41" width="14.296875" customWidth="1"/>
-    <col min="42" max="42" width="8.796875" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" customWidth="1"/>
+    <col min="15" max="16" width="12.77734375" customWidth="1"/>
+    <col min="17" max="17" width="14.21875" customWidth="1"/>
+    <col min="18" max="18" width="12.77734375" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="44" customWidth="1"/>
+    <col min="21" max="21" width="35.77734375" customWidth="1"/>
+    <col min="22" max="22" width="36.21875" customWidth="1"/>
+    <col min="23" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="14.88671875" customWidth="1"/>
+    <col min="26" max="26" width="14.44140625" customWidth="1"/>
+    <col min="27" max="27" width="15.21875" customWidth="1"/>
+    <col min="28" max="28" width="15.88671875" customWidth="1"/>
+    <col min="29" max="29" width="9.88671875" customWidth="1"/>
+    <col min="30" max="30" width="9.6640625" customWidth="1"/>
+    <col min="31" max="31" width="8.77734375" customWidth="1"/>
+    <col min="32" max="33" width="17" customWidth="1"/>
+    <col min="34" max="34" width="17.44140625" customWidth="1"/>
+    <col min="35" max="35" width="18.5546875" customWidth="1"/>
+    <col min="36" max="36" width="16.109375" customWidth="1"/>
+    <col min="38" max="38" width="13.6640625" customWidth="1"/>
+    <col min="39" max="39" width="56.21875" customWidth="1"/>
+    <col min="40" max="40" width="44.44140625" customWidth="1"/>
+    <col min="41" max="41" width="43.44140625" customWidth="1"/>
+    <col min="42" max="42" width="14.33203125" customWidth="1"/>
+    <col min="43" max="43" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -40822,11 +40822,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>62</v>
-      </c>
-      <c r="S1" t="s">
-        <v>42</v>
       </c>
       <c r="T1" t="s">
         <v>42</v>
@@ -40835,19 +40832,19 @@
         <v>42</v>
       </c>
       <c r="V1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" t="s">
         <v>63</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>63</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>64</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>42</v>
       </c>
       <c r="AM1" t="s">
         <v>42</v>
@@ -40855,8 +40852,11 @@
       <c r="AN1" t="s">
         <v>42</v>
       </c>
+      <c r="AO1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="B2" t="s">
         <v>65</v>
       </c>
@@ -40869,11 +40869,8 @@
       <c r="L2" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>63</v>
-      </c>
-      <c r="S2" t="s">
-        <v>43</v>
       </c>
       <c r="T2" t="s">
         <v>43</v>
@@ -40882,16 +40879,16 @@
         <v>43</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
         <v>63</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>44</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>63</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>66</v>
       </c>
       <c r="AG2" t="s">
         <v>66</v>
@@ -40903,10 +40900,10 @@
         <v>66</v>
       </c>
       <c r="AJ2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK2" t="s">
         <v>63</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>43</v>
       </c>
       <c r="AM2" t="s">
         <v>43</v>
@@ -40914,8 +40911,11 @@
       <c r="AN2" t="s">
         <v>43</v>
       </c>
+      <c r="AO2" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -40964,80 +40964,83 @@
       <c r="P3" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" t="s">
         <v>63</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>45</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>46</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>47</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>63</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>49</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>17</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>18</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>20</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>21</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
         <v>22</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AE3" t="s">
         <v>63</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>5</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AI3" t="s">
         <v>7</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AJ3" t="s">
         <v>58</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="AK3" t="s">
         <v>63</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AL3" t="s">
         <v>59</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AM3" t="s">
         <v>46</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>47</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AO3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -41084,82 +41087,85 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="Q4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="R4">
         <v>99833</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>26</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>0.13492199999999999</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0.13270399999999999</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>6.4148999999999998E-2</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>63</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>26</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>43.82</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>41.21</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>15.25</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>8.99</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>50.05</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>37.86</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>63</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>26</v>
       </c>
-      <c r="AF4">
+      <c r="AG4">
         <v>0.30197600000000002</v>
       </c>
-      <c r="AG4">
+      <c r="AH4">
         <v>0.36239900000000003</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>0.168013</v>
       </c>
-      <c r="AI4">
+      <c r="AJ4">
         <v>0.171043</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AK4" t="s">
         <v>63</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AL4" t="s">
         <v>26</v>
       </c>
-      <c r="AL4">
-        <f t="shared" ref="AL4:AL15" si="0">((S4*1000000)/(Q4))</f>
+      <c r="AM4">
+        <f t="shared" ref="AM4:AM15" si="0">((T4*1000000)/(R4))</f>
         <v>1.351476966534112</v>
       </c>
-      <c r="AM4">
-        <f t="shared" ref="AM4:AM15" si="1">((T4*1000000)/(Q4))</f>
+      <c r="AN4">
+        <f t="shared" ref="AN4:AN15" si="1">((U4*1000000)/(R4))</f>
         <v>1.3292598639728346</v>
       </c>
-      <c r="AN4">
-        <f t="shared" ref="AN4:AN15" si="2">((U4*1000000)/(Q4))</f>
+      <c r="AO4">
+        <f t="shared" ref="AO4:AO15" si="2">((V4*1000000)/(R4))</f>
         <v>0.64256308034417475</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -41206,82 +41212,85 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="Q5">
+        <v>0.13880999999999999</v>
+      </c>
+      <c r="R5">
         <v>89229</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>27</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>0.49547099999999999</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>0.62771500000000002</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0.45558799999999999</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>63</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>27</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>10.52</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>7.87</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>5.87</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>3.27</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>17.190000000000001</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>12.89</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>63</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>27</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>1.114933</v>
       </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>1.862663</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>0.468358</v>
       </c>
-      <c r="AI5">
+      <c r="AJ5">
         <v>0.31703999999999999</v>
       </c>
-      <c r="AJ5" t="s">
+      <c r="AK5" t="s">
         <v>63</v>
       </c>
-      <c r="AK5" t="s">
+      <c r="AL5" t="s">
         <v>27</v>
       </c>
-      <c r="AL5">
+      <c r="AM5">
         <f t="shared" si="0"/>
         <v>5.5528023400463971</v>
       </c>
-      <c r="AM5">
+      <c r="AN5">
         <f t="shared" si="1"/>
         <v>7.0348765535868383</v>
       </c>
-      <c r="AN5">
+      <c r="AO5">
         <f t="shared" si="2"/>
         <v>5.1058288224680313</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -41328,82 +41337,85 @@
         <v>0.111</v>
       </c>
       <c r="Q6">
+        <v>0.13868</v>
+      </c>
+      <c r="R6">
         <v>99859</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>28</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>0.156301</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.121558</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>0.173295</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>63</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>28</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>42.83</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>29.41</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>13.86</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>4.3499999999999996</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <v>49.24</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>26.95</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>63</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>28</v>
       </c>
-      <c r="AF6">
+      <c r="AG6">
         <v>0.458679</v>
       </c>
-      <c r="AG6">
+      <c r="AH6">
         <v>1.1434880000000001</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>0.194274</v>
       </c>
-      <c r="AI6">
+      <c r="AJ6">
         <v>0.17954999999999999</v>
       </c>
-      <c r="AJ6" t="s">
+      <c r="AK6" t="s">
         <v>63</v>
       </c>
-      <c r="AK6" t="s">
+      <c r="AL6" t="s">
         <v>28</v>
       </c>
-      <c r="AL6">
+      <c r="AM6">
         <f t="shared" si="0"/>
         <v>1.5652169559078299</v>
       </c>
-      <c r="AM6">
+      <c r="AN6">
         <f t="shared" si="1"/>
         <v>1.2172963879069487</v>
       </c>
-      <c r="AN6">
+      <c r="AO6">
         <f t="shared" si="2"/>
         <v>1.7353969096425961</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -41450,82 +41462,85 @@
         <v>0.184</v>
       </c>
       <c r="Q7">
+        <v>0.13877</v>
+      </c>
+      <c r="R7">
         <v>99882</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>29</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>0.23811299999999999</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>0.18201800000000001</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>0.134715</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>63</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>29</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>36.270000000000003</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>25.59</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>14.23</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>5.09</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>35.340000000000003</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>30.18</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>63</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>29</v>
       </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>0.49727700000000002</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>1.292597</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>0.19742999999999999</v>
       </c>
-      <c r="AI7">
+      <c r="AJ7">
         <v>0.16584599999999999</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AK7" t="s">
         <v>63</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AL7" t="s">
         <v>29</v>
       </c>
-      <c r="AL7">
+      <c r="AM7">
         <f t="shared" si="0"/>
         <v>2.3839430528023069</v>
       </c>
-      <c r="AM7">
+      <c r="AN7">
         <f t="shared" si="1"/>
         <v>1.822330349812779</v>
       </c>
-      <c r="AN7">
+      <c r="AO7">
         <f t="shared" si="2"/>
         <v>1.3487415149876856</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -41571,83 +41586,83 @@
       <c r="O8">
         <v>0.17699999999999999</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>99409</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>30</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>0.25917600000000002</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>0.105781</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>8.7622000000000005E-2</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>63</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>30</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>34.130000000000003</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <v>29.08</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>17.13</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>7.07</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <v>32.58</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>37.74</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>63</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>30</v>
       </c>
-      <c r="AF8">
+      <c r="AG8">
         <v>0.363174</v>
       </c>
-      <c r="AG8">
+      <c r="AH8">
         <v>0.43487799999999999</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>0.29427900000000001</v>
       </c>
-      <c r="AI8">
+      <c r="AJ8">
         <v>0.190941</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AK8" t="s">
         <v>63</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AL8" t="s">
         <v>30</v>
       </c>
-      <c r="AL8">
+      <c r="AM8">
         <f t="shared" si="0"/>
         <v>2.6071683650373711</v>
       </c>
-      <c r="AM8">
+      <c r="AN8">
         <f t="shared" si="1"/>
         <v>1.0640988240501363</v>
       </c>
-      <c r="AN8">
+      <c r="AO8">
         <f t="shared" si="2"/>
         <v>0.88142924684887691</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -41694,82 +41709,85 @@
         <v>0.21</v>
       </c>
       <c r="Q9">
+        <v>0.14387</v>
+      </c>
+      <c r="R9">
         <v>96376</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>31</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>0.30909999999999999</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>0.18318899999999999</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>0.148593</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
         <v>63</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>31</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>29.31</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>17.190000000000001</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>9.07</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>3.07</v>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <v>26.94</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>21.36</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>63</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AF9" t="s">
         <v>31</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>0.313581</v>
       </c>
-      <c r="AG9">
+      <c r="AH9">
         <v>1.0231840000000001</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>0.23905699999999999</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <v>0.19268199999999999</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AK9" t="s">
         <v>63</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AL9" t="s">
         <v>31</v>
       </c>
-      <c r="AL9">
+      <c r="AM9">
         <f t="shared" si="0"/>
         <v>3.2072300157715614</v>
       </c>
-      <c r="AM9">
+      <c r="AN9">
         <f t="shared" si="1"/>
         <v>1.9007740516311116</v>
       </c>
-      <c r="AN9">
+      <c r="AO9">
         <f t="shared" si="2"/>
         <v>1.5418050136963559</v>
       </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -41816,82 +41834,85 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="Q10">
+        <v>0.13553999999999999</v>
+      </c>
+      <c r="R10">
         <v>98555</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>32</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>0.200548</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>0.13469700000000001</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>8.4551000000000001E-2</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>63</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>32</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>27.48</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>23.54</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>11.58</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <v>33.590000000000003</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>23.95</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="s">
         <v>63</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>32</v>
       </c>
-      <c r="AF10">
+      <c r="AG10">
         <v>0.37761299999999998</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>0.51433200000000001</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>0.18240899999999999</v>
       </c>
-      <c r="AI10">
+      <c r="AJ10">
         <v>0.156449</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AK10" t="s">
         <v>63</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AL10" t="s">
         <v>32</v>
       </c>
-      <c r="AL10">
+      <c r="AM10">
         <f t="shared" si="0"/>
         <v>2.0348840748820454</v>
       </c>
-      <c r="AM10">
+      <c r="AN10">
         <f t="shared" si="1"/>
         <v>1.3667190908629698</v>
       </c>
-      <c r="AN10">
+      <c r="AO10">
         <f t="shared" si="2"/>
         <v>0.8579067525747045</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -41938,82 +41959,85 @@
         <v>0.183</v>
       </c>
       <c r="Q11">
+        <v>0.13649</v>
+      </c>
+      <c r="R11">
         <v>92932</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>33</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>0.28535700000000003</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>0.13481099999999999</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>0.130994</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
         <v>63</v>
       </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>33</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>33.86</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>18.2</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>8.9700000000000006</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>7.78</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>35.01</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>30.24</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AE11" t="s">
         <v>63</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AF11" t="s">
         <v>33</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>0.30224800000000002</v>
       </c>
-      <c r="AG11">
+      <c r="AH11">
         <v>0.51481699999999997</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>0.25740400000000002</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <v>0.19232199999999999</v>
       </c>
-      <c r="AJ11" t="s">
+      <c r="AK11" t="s">
         <v>63</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AL11" t="s">
         <v>33</v>
       </c>
-      <c r="AL11">
+      <c r="AM11">
         <f t="shared" si="0"/>
         <v>3.0706000086084448</v>
       </c>
-      <c r="AM11">
+      <c r="AN11">
         <f t="shared" si="1"/>
         <v>1.4506413291438902</v>
       </c>
-      <c r="AN11">
+      <c r="AO11">
         <f t="shared" si="2"/>
         <v>1.4095682864890458</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -42060,82 +42084,85 @@
         <v>0.222</v>
       </c>
       <c r="Q12">
+        <v>0.14011000000000001</v>
+      </c>
+      <c r="R12">
         <v>92765</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>34</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>0.22174099999999999</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0.129131</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>0.16089999999999999</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W12" t="s">
         <v>63</v>
       </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>34</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>28.1</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>10.42</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>3.22</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>2.63</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>31.45</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>14</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>63</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AF12" t="s">
         <v>34</v>
       </c>
-      <c r="AF12">
+      <c r="AG12">
         <v>0.839835</v>
       </c>
-      <c r="AG12">
+      <c r="AH12">
         <v>0.915161</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>0.194441</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <v>0.245118</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AK12" t="s">
         <v>63</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AL12" t="s">
         <v>34</v>
       </c>
-      <c r="AL12">
+      <c r="AM12">
         <f t="shared" si="0"/>
         <v>2.390351964641837</v>
       </c>
-      <c r="AM12">
+      <c r="AN12">
         <f t="shared" si="1"/>
         <v>1.3920228534468819</v>
       </c>
-      <c r="AN12">
+      <c r="AO12">
         <f t="shared" si="2"/>
         <v>1.7344903789144612</v>
       </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -42182,82 +42209,85 @@
         <v>0.17</v>
       </c>
       <c r="Q13">
+        <v>0.13849</v>
+      </c>
+      <c r="R13">
         <v>93324</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>35</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>0.24881600000000001</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>0.12670200000000001</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>0.15800500000000001</v>
       </c>
-      <c r="V13" t="s">
+      <c r="W13" t="s">
         <v>63</v>
       </c>
-      <c r="W13" t="s">
+      <c r="X13" t="s">
         <v>35</v>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <v>31.05</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <v>20.23</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>7.75</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>5.24</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>39.26</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>29.96</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="s">
         <v>63</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AF13" t="s">
         <v>35</v>
       </c>
-      <c r="AF13">
+      <c r="AG13">
         <v>0.293904</v>
       </c>
-      <c r="AG13">
+      <c r="AH13">
         <v>0.80602300000000004</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>0.23652999999999999</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <v>0.18124699999999999</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AK13" t="s">
         <v>63</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AL13" t="s">
         <v>35</v>
       </c>
-      <c r="AL13">
+      <c r="AM13">
         <f t="shared" si="0"/>
         <v>2.666152329518666</v>
       </c>
-      <c r="AM13">
+      <c r="AN13">
         <f t="shared" si="1"/>
         <v>1.3576571942908577</v>
       </c>
-      <c r="AN13">
+      <c r="AO13">
         <f t="shared" si="2"/>
         <v>1.6930800222879432</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -42304,82 +42334,85 @@
         <v>0.154</v>
       </c>
       <c r="Q14">
+        <v>0.13735</v>
+      </c>
+      <c r="R14">
         <v>99782</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>36</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>0.206486</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>0.120281</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>0.24107300000000001</v>
       </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
         <v>63</v>
       </c>
-      <c r="W14" t="s">
+      <c r="X14" t="s">
         <v>36</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>32.31</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>27.42</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>8.06</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>2.59</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>33.11</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>30.25</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AE14" t="s">
         <v>63</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AF14" t="s">
         <v>36</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>0.70822300000000005</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
         <v>1.81484</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>0.19484099999999999</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>0.179868</v>
       </c>
-      <c r="AJ14" t="s">
+      <c r="AK14" t="s">
         <v>63</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AL14" t="s">
         <v>36</v>
       </c>
-      <c r="AL14">
+      <c r="AM14">
         <f t="shared" si="0"/>
         <v>2.0693712292798301</v>
       </c>
-      <c r="AM14">
+      <c r="AN14">
         <f t="shared" si="1"/>
         <v>1.2054378545228599</v>
       </c>
-      <c r="AN14">
+      <c r="AO14">
         <f t="shared" si="2"/>
         <v>2.41599687318354</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -42425,129 +42458,129 @@
       <c r="O15">
         <v>0.12</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>100000</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>37</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>0.176928</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>9.1879000000000002E-2</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0.13399900000000001</v>
       </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
         <v>63</v>
       </c>
-      <c r="W15" t="s">
+      <c r="X15" t="s">
         <v>37</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>38.590000000000003</v>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <v>37.799999999999997</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>13.59</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>7.18</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>33.1</v>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <v>26.31</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AE15" t="s">
         <v>63</v>
       </c>
-      <c r="AE15" t="s">
+      <c r="AF15" t="s">
         <v>37</v>
       </c>
-      <c r="AF15">
+      <c r="AG15">
         <v>0.250637</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
         <v>0.28578599999999998</v>
       </c>
-      <c r="AH15">
+      <c r="AI15">
         <v>0.20114499999999999</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <v>0.197049</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AK15" t="s">
         <v>63</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AL15" t="s">
         <v>37</v>
       </c>
-      <c r="AL15">
+      <c r="AM15">
         <f t="shared" si="0"/>
         <v>1.76928</v>
       </c>
-      <c r="AM15">
+      <c r="AN15">
         <f t="shared" si="1"/>
         <v>0.91879</v>
       </c>
-      <c r="AN15">
+      <c r="AO15">
         <f t="shared" si="2"/>
         <v>1.33999</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
-      <c r="Q16" t="s">
+    <row r="16" spans="1:41">
+      <c r="R16" t="s">
         <v>63</v>
       </c>
-      <c r="V16" t="s">
+      <c r="W16" t="s">
         <v>63</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AE16" t="s">
         <v>63</v>
       </c>
-      <c r="AJ16" t="s">
+      <c r="AK16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>63</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>50</v>
       </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
         <v>63</v>
       </c>
-      <c r="W17" t="s">
+      <c r="X17" t="s">
         <v>51</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AE17" t="s">
         <v>63</v>
       </c>
-      <c r="AE17" t="s">
+      <c r="AF17" t="s">
         <v>57</v>
       </c>
-      <c r="AJ17" t="s">
+      <c r="AK17" t="s">
         <v>63</v>
       </c>
-      <c r="AK17" t="s">
+      <c r="AL17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -42590,83 +42623,83 @@
       <c r="P18">
         <v>1380</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>99833</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>26</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>5589591</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>2424363</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>2427591</v>
       </c>
-      <c r="V18" t="s">
+      <c r="W18" t="s">
         <v>63</v>
       </c>
-      <c r="W18" t="s">
+      <c r="X18" t="s">
         <v>26</v>
       </c>
-      <c r="X18">
+      <c r="Y18">
         <v>15.85</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>19.82</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>16.62</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>20.91</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>13.05</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>20.260000000000002</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AE18" t="s">
         <v>63</v>
       </c>
-      <c r="AE18" t="s">
+      <c r="AF18" t="s">
         <v>26</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>2021.8242190000001</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>4806.890625</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>5459.6337890000004</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <v>524.42578100000003</v>
       </c>
-      <c r="AJ18" t="s">
+      <c r="AK18" t="s">
         <v>63</v>
       </c>
-      <c r="AK18" t="s">
+      <c r="AL18" t="s">
         <v>26</v>
       </c>
-      <c r="AL18">
-        <f t="shared" ref="AL18:AL29" si="3">S18/1000</f>
+      <c r="AM18">
+        <f t="shared" ref="AM18:AM29" si="3">T18/1000</f>
         <v>5589.5910000000003</v>
       </c>
-      <c r="AM18">
-        <f t="shared" ref="AM18:AM29" si="4">T18/1000</f>
+      <c r="AN18">
+        <f t="shared" ref="AN18:AN29" si="4">U18/1000</f>
         <v>2424.3629999999998</v>
       </c>
-      <c r="AN18">
-        <f t="shared" ref="AN18:AN29" si="5">U18/1000</f>
+      <c r="AO18">
+        <f t="shared" ref="AO18:AO29" si="5">V18/1000</f>
         <v>2427.5909999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -42709,83 +42742,83 @@
       <c r="P19">
         <v>13900</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>89229</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>27</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>4756746</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>2182451</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>2173151</v>
       </c>
-      <c r="V19" t="s">
+      <c r="W19" t="s">
         <v>63</v>
       </c>
-      <c r="W19" t="s">
+      <c r="X19" t="s">
         <v>27</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>12.32</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <v>23.1</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>12.97</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>24.7</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>91.06</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>165.74</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AE19" t="s">
         <v>63</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AF19" t="s">
         <v>27</v>
       </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>2323.4570309999999</v>
       </c>
-      <c r="AG19">
+      <c r="AH19">
         <v>4306.7382809999999</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>4642.3369140000004</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <v>632.83886700000005</v>
       </c>
-      <c r="AJ19" t="s">
+      <c r="AK19" t="s">
         <v>63</v>
       </c>
-      <c r="AK19" t="s">
+      <c r="AL19" t="s">
         <v>27</v>
       </c>
-      <c r="AL19">
+      <c r="AM19">
         <f t="shared" si="3"/>
         <v>4756.7460000000001</v>
       </c>
-      <c r="AM19">
+      <c r="AN19">
         <f t="shared" si="4"/>
         <v>2182.451</v>
       </c>
-      <c r="AN19">
+      <c r="AO19">
         <f t="shared" si="5"/>
         <v>2173.1509999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -42828,83 +42861,83 @@
       <c r="P20">
         <v>1480</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>99859</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>28</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>5592716</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>2440173</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>2444361</v>
       </c>
-      <c r="V20" t="s">
+      <c r="W20" t="s">
         <v>63</v>
       </c>
-      <c r="W20" t="s">
+      <c r="X20" t="s">
         <v>28</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>15.87</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <v>24.76</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>17.059999999999999</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>25.99</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>12.04</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>24.47</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="s">
         <v>63</v>
       </c>
-      <c r="AE20" t="s">
+      <c r="AF20" t="s">
         <v>28</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>2030.5664059999999</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>4826.6367190000001</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>5462.3427730000003</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <v>1063.3701169999999</v>
       </c>
-      <c r="AJ20" t="s">
+      <c r="AK20" t="s">
         <v>63</v>
       </c>
-      <c r="AK20" t="s">
+      <c r="AL20" t="s">
         <v>28</v>
       </c>
-      <c r="AL20">
+      <c r="AM20">
         <f t="shared" si="3"/>
         <v>5592.7160000000003</v>
       </c>
-      <c r="AM20">
+      <c r="AN20">
         <f t="shared" si="4"/>
         <v>2440.1729999999998</v>
       </c>
-      <c r="AN20">
+      <c r="AO20">
         <f t="shared" si="5"/>
         <v>2444.3609999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -42947,83 +42980,83 @@
       <c r="P21">
         <v>1604</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>99882</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>29</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>5599753</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>2443990</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>2456166</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
         <v>63</v>
       </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>29</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>15.89</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>24.29</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>16.66</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>25.35</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>12.43</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>24.3</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>63</v>
       </c>
-      <c r="AE21" t="s">
+      <c r="AF21" t="s">
         <v>29</v>
       </c>
-      <c r="AF21">
+      <c r="AG21">
         <v>2222.4726559999999</v>
       </c>
-      <c r="AG21">
+      <c r="AH21">
         <v>4818.28125</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>5469.4560549999997</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>1096.1835940000001</v>
       </c>
-      <c r="AJ21" t="s">
+      <c r="AK21" t="s">
         <v>63</v>
       </c>
-      <c r="AK21" t="s">
+      <c r="AL21" t="s">
         <v>29</v>
       </c>
-      <c r="AL21">
+      <c r="AM21">
         <f t="shared" si="3"/>
         <v>5599.7529999999997</v>
       </c>
-      <c r="AM21">
+      <c r="AN21">
         <f t="shared" si="4"/>
         <v>2443.9899999999998</v>
       </c>
-      <c r="AN21">
+      <c r="AO21">
         <f t="shared" si="5"/>
         <v>2456.1660000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -43066,83 +43099,83 @@
       <c r="P22">
         <v>1058</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>99409</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>30</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>5656013</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>2439091</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>2425679</v>
       </c>
-      <c r="V22" t="s">
+      <c r="W22" t="s">
         <v>63</v>
       </c>
-      <c r="W22" t="s">
+      <c r="X22" t="s">
         <v>30</v>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <v>14.86</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
         <v>17.989999999999998</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>16.239999999999998</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>19.920000000000002</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>13.79</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>17.39</v>
       </c>
-      <c r="AD22" t="s">
+      <c r="AE22" t="s">
         <v>63</v>
       </c>
-      <c r="AE22" t="s">
+      <c r="AF22" t="s">
         <v>30</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>2557.8359380000002</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>4796.2617190000001</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>5444.9472660000001</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>503.69726600000001</v>
       </c>
-      <c r="AJ22" t="s">
+      <c r="AK22" t="s">
         <v>63</v>
       </c>
-      <c r="AK22" t="s">
+      <c r="AL22" t="s">
         <v>30</v>
       </c>
-      <c r="AL22">
+      <c r="AM22">
         <f t="shared" si="3"/>
         <v>5656.0129999999999</v>
       </c>
-      <c r="AM22">
+      <c r="AN22">
         <f t="shared" si="4"/>
         <v>2439.0909999999999</v>
       </c>
-      <c r="AN22">
+      <c r="AO22">
         <f t="shared" si="5"/>
         <v>2425.6790000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -43185,83 +43218,83 @@
       <c r="P23">
         <v>1663</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>96376</v>
       </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>31</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>5399003</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>2335768</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>2326628</v>
       </c>
-      <c r="V23" t="s">
+      <c r="W23" t="s">
         <v>63</v>
       </c>
-      <c r="W23" t="s">
+      <c r="X23" t="s">
         <v>31</v>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <v>15.5</v>
       </c>
-      <c r="Y23">
+      <c r="Z23">
         <v>38.450000000000003</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>15.87</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>54.34</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>12.84</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>56.3</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AE23" t="s">
         <v>63</v>
       </c>
-      <c r="AE23" t="s">
+      <c r="AF23" t="s">
         <v>31</v>
       </c>
-      <c r="AF23">
+      <c r="AG23">
         <v>2066.0351559999999</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>4655.6015619999998</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>5273.9091799999997</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>510.13574199999999</v>
       </c>
-      <c r="AJ23" t="s">
+      <c r="AK23" t="s">
         <v>63</v>
       </c>
-      <c r="AK23" t="s">
+      <c r="AL23" t="s">
         <v>31</v>
       </c>
-      <c r="AL23">
+      <c r="AM23">
         <f t="shared" si="3"/>
         <v>5399.0029999999997</v>
       </c>
-      <c r="AM23">
+      <c r="AN23">
         <f t="shared" si="4"/>
         <v>2335.768</v>
       </c>
-      <c r="AN23">
+      <c r="AO23">
         <f t="shared" si="5"/>
         <v>2326.6280000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -43304,83 +43337,83 @@
       <c r="P24">
         <v>1486</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>98555</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>32</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>5522407</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>2406181</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>2422489</v>
       </c>
-      <c r="V24" t="s">
+      <c r="W24" t="s">
         <v>63</v>
       </c>
-      <c r="W24" t="s">
+      <c r="X24" t="s">
         <v>32</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>15.79</v>
       </c>
-      <c r="Y24">
+      <c r="Z24">
         <v>24.91</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>14.69</v>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <v>25.41</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>18.52</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>32.6</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>63</v>
       </c>
-      <c r="AE24" t="s">
+      <c r="AF24" t="s">
         <v>32</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>2168.7265619999998</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>4742.2773440000001</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>5386.3271480000003</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>199.52246099999999</v>
       </c>
-      <c r="AJ24" t="s">
+      <c r="AK24" t="s">
         <v>63</v>
       </c>
-      <c r="AK24" t="s">
+      <c r="AL24" t="s">
         <v>32</v>
       </c>
-      <c r="AL24">
+      <c r="AM24">
         <f t="shared" si="3"/>
         <v>5522.4070000000002</v>
       </c>
-      <c r="AM24">
+      <c r="AN24">
         <f t="shared" si="4"/>
         <v>2406.181</v>
       </c>
-      <c r="AN24">
+      <c r="AO24">
         <f t="shared" si="5"/>
         <v>2422.489</v>
       </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -43423,83 +43456,83 @@
       <c r="P25">
         <v>2380</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>92932</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>33</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>5201805</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>2241968</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>2259912</v>
       </c>
-      <c r="V25" t="s">
+      <c r="W25" t="s">
         <v>63</v>
       </c>
-      <c r="W25" t="s">
+      <c r="X25" t="s">
         <v>33</v>
       </c>
-      <c r="X25">
+      <c r="Y25">
         <v>14.84</v>
       </c>
-      <c r="Y25">
+      <c r="Z25">
         <v>31.68</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>14.84</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>43.38</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>12.07</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>32.24</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" t="s">
         <v>63</v>
       </c>
-      <c r="AE25" t="s">
+      <c r="AF25" t="s">
         <v>33</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>1708.84375</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>4483.0703119999998</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>5101.5859380000002</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <v>253.570312</v>
       </c>
-      <c r="AJ25" t="s">
+      <c r="AK25" t="s">
         <v>63</v>
       </c>
-      <c r="AK25" t="s">
+      <c r="AL25" t="s">
         <v>33</v>
       </c>
-      <c r="AL25">
+      <c r="AM25">
         <f t="shared" si="3"/>
         <v>5201.8050000000003</v>
       </c>
-      <c r="AM25">
+      <c r="AN25">
         <f t="shared" si="4"/>
         <v>2241.9679999999998</v>
       </c>
-      <c r="AN25">
+      <c r="AO25">
         <f t="shared" si="5"/>
         <v>2259.9119999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -43542,83 +43575,83 @@
       <c r="P26">
         <v>8693</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>92765</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>34</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>5206347</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>2240235</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>2265431</v>
       </c>
-      <c r="V26" t="s">
+      <c r="W26" t="s">
         <v>63</v>
       </c>
-      <c r="W26" t="s">
+      <c r="X26" t="s">
         <v>34</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
         <v>14.86</v>
       </c>
-      <c r="Y26">
+      <c r="Z26">
         <v>64.790000000000006</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>13.14</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>83.28</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>17.989999999999998</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>505.9</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>63</v>
       </c>
-      <c r="AE26" t="s">
+      <c r="AF26" t="s">
         <v>34</v>
       </c>
-      <c r="AF26">
+      <c r="AG26">
         <v>1267.7070309999999</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>4465.4101559999999</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>5071.1660160000001</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <v>39516.113280999998</v>
       </c>
-      <c r="AJ26" t="s">
+      <c r="AK26" t="s">
         <v>63</v>
       </c>
-      <c r="AK26" t="s">
+      <c r="AL26" t="s">
         <v>34</v>
       </c>
-      <c r="AL26">
+      <c r="AM26">
         <f t="shared" si="3"/>
         <v>5206.3469999999998</v>
       </c>
-      <c r="AM26">
+      <c r="AN26">
         <f t="shared" si="4"/>
         <v>2240.2350000000001</v>
       </c>
-      <c r="AN26">
+      <c r="AO26">
         <f t="shared" si="5"/>
         <v>2265.431</v>
       </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -43661,83 +43694,83 @@
       <c r="P27">
         <v>1825</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>93324</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>35</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>5221944</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>2267088</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>2273344</v>
       </c>
-      <c r="V27" t="s">
+      <c r="W27" t="s">
         <v>63</v>
       </c>
-      <c r="W27" t="s">
+      <c r="X27" t="s">
         <v>35</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>15.31</v>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <v>27.16</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>15.36</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>35.46</v>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <v>12.93</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>50.74</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
         <v>63</v>
       </c>
-      <c r="AE27" t="s">
+      <c r="AF27" t="s">
         <v>35</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>2158.9101559999999</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>4498.1210940000001</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>5095.0986329999996</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <v>372.328125</v>
       </c>
-      <c r="AJ27" t="s">
+      <c r="AK27" t="s">
         <v>63</v>
       </c>
-      <c r="AK27" t="s">
+      <c r="AL27" t="s">
         <v>35</v>
       </c>
-      <c r="AL27">
+      <c r="AM27">
         <f t="shared" si="3"/>
         <v>5221.9440000000004</v>
       </c>
-      <c r="AM27">
+      <c r="AN27">
         <f t="shared" si="4"/>
         <v>2267.0880000000002</v>
       </c>
-      <c r="AN27">
+      <c r="AO27">
         <f t="shared" si="5"/>
         <v>2273.3440000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -43780,83 +43813,83 @@
       <c r="P28">
         <v>1792</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>99782</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>36</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>5588642</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>2456790</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>2406114</v>
       </c>
-      <c r="V28" t="s">
+      <c r="W28" t="s">
         <v>63</v>
       </c>
-      <c r="W28" t="s">
+      <c r="X28" t="s">
         <v>36</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
         <v>15.83</v>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <v>19.64</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>16.79</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>20.96</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>25.23</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>29.56</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>63</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AF28" t="s">
         <v>36</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>1958.2773440000001</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>4800.6601559999999</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>5458.1650390000004</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <v>1126.993164</v>
       </c>
-      <c r="AJ28" t="s">
+      <c r="AK28" t="s">
         <v>63</v>
       </c>
-      <c r="AK28" t="s">
+      <c r="AL28" t="s">
         <v>36</v>
       </c>
-      <c r="AL28">
+      <c r="AM28">
         <f t="shared" si="3"/>
         <v>5588.6419999999998</v>
       </c>
-      <c r="AM28">
+      <c r="AN28">
         <f t="shared" si="4"/>
         <v>2456.79</v>
       </c>
-      <c r="AN28">
+      <c r="AO28">
         <f t="shared" si="5"/>
         <v>2406.114</v>
       </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -43899,126 +43932,126 @@
       <c r="P29">
         <v>1343</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>100000</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>37</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>5546482</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>2414712</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>2449584</v>
       </c>
-      <c r="V29" t="s">
+      <c r="W29" t="s">
         <v>63</v>
       </c>
-      <c r="W29" t="s">
+      <c r="X29" t="s">
         <v>37</v>
-      </c>
-      <c r="X29">
-        <v>15.99</v>
       </c>
       <c r="Y29">
         <v>15.99</v>
       </c>
       <c r="Z29">
+        <v>15.99</v>
+      </c>
+      <c r="AA29">
         <v>16.55</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>16.760000000000002</v>
-      </c>
-      <c r="AB29">
-        <v>16.96</v>
       </c>
       <c r="AC29">
         <v>16.96</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AD29">
+        <v>16.96</v>
+      </c>
+      <c r="AE29" t="s">
         <v>63</v>
       </c>
-      <c r="AE29" t="s">
+      <c r="AF29" t="s">
         <v>37</v>
       </c>
-      <c r="AF29">
+      <c r="AG29">
         <v>1597.1953120000001</v>
       </c>
-      <c r="AG29">
+      <c r="AH29">
         <v>4811.0625</v>
       </c>
-      <c r="AH29">
+      <c r="AI29">
         <v>5417.0048829999996</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <v>208.92089799999999</v>
       </c>
-      <c r="AJ29" t="s">
+      <c r="AK29" t="s">
         <v>63</v>
       </c>
-      <c r="AK29" t="s">
+      <c r="AL29" t="s">
         <v>37</v>
       </c>
-      <c r="AL29">
+      <c r="AM29">
         <f t="shared" si="3"/>
         <v>5546.482</v>
       </c>
-      <c r="AM29">
+      <c r="AN29">
         <f t="shared" si="4"/>
         <v>2414.712</v>
       </c>
-      <c r="AN29">
+      <c r="AO29">
         <f t="shared" si="5"/>
         <v>2449.5839999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:40">
-      <c r="Q30" t="s">
+    <row r="30" spans="1:41">
+      <c r="R30" t="s">
         <v>63</v>
       </c>
-      <c r="V30" t="s">
+      <c r="W30" t="s">
         <v>63</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>63</v>
       </c>
-      <c r="AJ30" t="s">
+      <c r="AK30" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>63</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" t="s">
         <v>52</v>
       </c>
-      <c r="V31" t="s">
+      <c r="W31" t="s">
         <v>63</v>
       </c>
-      <c r="W31" t="s">
+      <c r="X31" t="s">
         <v>53</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>63</v>
       </c>
-      <c r="AE31" t="s">
+      <c r="AF31" t="s">
         <v>60</v>
       </c>
-      <c r="AJ31" t="s">
+      <c r="AK31" t="s">
         <v>63</v>
       </c>
-      <c r="AK31" t="s">
+      <c r="AL31" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -44052,74 +44085,74 @@
       <c r="M32">
         <v>0.21958</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>99833</v>
       </c>
-      <c r="R32" t="s">
+      <c r="S32" t="s">
         <v>26</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>43.069600000000001</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>46.117600000000003</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>43.492199999999997</v>
       </c>
-      <c r="V32" t="s">
+      <c r="W32" t="s">
         <v>63</v>
       </c>
-      <c r="W32" t="s">
+      <c r="X32" t="s">
         <v>26</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
         <v>10.1</v>
       </c>
-      <c r="Y32">
+      <c r="Z32">
         <v>6.53</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>5.78</v>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <v>7.95</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>63</v>
       </c>
-      <c r="AE32" t="s">
+      <c r="AF32" t="s">
         <v>26</v>
       </c>
-      <c r="AF32">
+      <c r="AG32">
         <v>0.52526899999999999</v>
       </c>
-      <c r="AG32">
+      <c r="AH32">
         <v>0.25629200000000002</v>
       </c>
-      <c r="AH32">
+      <c r="AI32">
         <v>0.84289899999999995</v>
       </c>
-      <c r="AJ32" t="s">
+      <c r="AK32" t="s">
         <v>63</v>
       </c>
-      <c r="AK32" t="s">
+      <c r="AL32" t="s">
         <v>26</v>
       </c>
-      <c r="AL32">
-        <f t="shared" ref="AL32:AL43" si="6">((S32*1000)/(Q32*0.5))</f>
+      <c r="AM32">
+        <f t="shared" ref="AM32:AM43" si="6">((T32*1000)/(R32*0.5))</f>
         <v>0.86283293099476122</v>
       </c>
-      <c r="AM32">
-        <f t="shared" ref="AM32:AM43" si="7">((T32*1000)/(Q32*0.5))</f>
+      <c r="AN32">
+        <f t="shared" ref="AN32:AN43" si="7">((U32*1000)/(R32*0.5))</f>
         <v>0.92389490449049927</v>
       </c>
-      <c r="AN32">
-        <f t="shared" ref="AN32:AN43" si="8">((U32*1000)/(Q32*0.5))</f>
+      <c r="AO32">
+        <f t="shared" ref="AO32:AO43" si="8">((V32*1000)/(R32*0.5))</f>
         <v>0.87129906944597468</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -44153,74 +44186,74 @@
       <c r="M33">
         <v>0.45832000000000001</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>89229</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
         <v>27</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>55.271799999999999</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>101.3278</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>97.014099999999999</v>
       </c>
-      <c r="V33" t="s">
+      <c r="W33" t="s">
         <v>63</v>
       </c>
-      <c r="W33" t="s">
+      <c r="X33" t="s">
         <v>27</v>
       </c>
-      <c r="X33">
+      <c r="Y33">
         <v>8.15</v>
       </c>
-      <c r="Y33">
+      <c r="Z33">
         <v>4.6500000000000004</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>4.29</v>
       </c>
-      <c r="AA33">
+      <c r="AB33">
         <v>5.1100000000000003</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>63</v>
       </c>
-      <c r="AE33" t="s">
+      <c r="AF33" t="s">
         <v>27</v>
       </c>
-      <c r="AF33">
+      <c r="AG33">
         <v>0.50329900000000005</v>
       </c>
-      <c r="AG33">
+      <c r="AH33">
         <v>0.24745700000000001</v>
       </c>
-      <c r="AH33">
+      <c r="AI33">
         <v>0.86837200000000003</v>
       </c>
-      <c r="AJ33" t="s">
+      <c r="AK33" t="s">
         <v>63</v>
       </c>
-      <c r="AK33" t="s">
+      <c r="AL33" t="s">
         <v>27</v>
       </c>
-      <c r="AL33">
+      <c r="AM33">
         <f t="shared" si="6"/>
         <v>1.2388752535610619</v>
       </c>
-      <c r="AM33">
+      <c r="AN33">
         <f t="shared" si="7"/>
         <v>2.2711853769514394</v>
       </c>
-      <c r="AN33">
+      <c r="AO33">
         <f t="shared" si="8"/>
         <v>2.1744970805455628</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -44254,74 +44287,74 @@
       <c r="M34">
         <v>0.24041999999999999</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>99859</v>
       </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>28</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>41.269799999999996</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>45.599200000000003</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>47.015799999999999</v>
       </c>
-      <c r="V34" t="s">
+      <c r="W34" t="s">
         <v>63</v>
       </c>
-      <c r="W34" t="s">
+      <c r="X34" t="s">
         <v>28</v>
       </c>
-      <c r="X34">
+      <c r="Y34">
         <v>12.64</v>
       </c>
-      <c r="Y34">
+      <c r="Z34">
         <v>5.51</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>6.67</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>6.64</v>
       </c>
-      <c r="AD34" t="s">
+      <c r="AE34" t="s">
         <v>63</v>
       </c>
-      <c r="AE34" t="s">
+      <c r="AF34" t="s">
         <v>28</v>
       </c>
-      <c r="AF34">
+      <c r="AG34">
         <v>0.39064599999999999</v>
       </c>
-      <c r="AG34">
+      <c r="AH34">
         <v>0.22734799999999999</v>
       </c>
-      <c r="AH34">
+      <c r="AI34">
         <v>0.92323699999999997</v>
       </c>
-      <c r="AJ34" t="s">
+      <c r="AK34" t="s">
         <v>63</v>
       </c>
-      <c r="AK34" t="s">
+      <c r="AL34" t="s">
         <v>28</v>
       </c>
-      <c r="AL34">
+      <c r="AM34">
         <f t="shared" si="6"/>
         <v>0.82656145164682193</v>
       </c>
-      <c r="AM34">
+      <c r="AN34">
         <f t="shared" si="7"/>
         <v>0.91327171311549293</v>
       </c>
-      <c r="AN34">
+      <c r="AO34">
         <f t="shared" si="8"/>
         <v>0.94164371764187493</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:41">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -44355,74 +44388,74 @@
       <c r="M35">
         <v>0.21021999999999999</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>99882</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
         <v>29</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>46.3658</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>63.6616</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>82.915800000000004</v>
       </c>
-      <c r="V35" t="s">
+      <c r="W35" t="s">
         <v>63</v>
       </c>
-      <c r="W35" t="s">
+      <c r="X35" t="s">
         <v>29</v>
       </c>
-      <c r="X35">
+      <c r="Y35">
         <v>12.89</v>
       </c>
-      <c r="Y35">
+      <c r="Z35">
         <v>5.23</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>6.92</v>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <v>7.41</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AE35" t="s">
         <v>63</v>
       </c>
-      <c r="AE35" t="s">
+      <c r="AF35" t="s">
         <v>29</v>
       </c>
-      <c r="AF35">
+      <c r="AG35">
         <v>0.39323999999999998</v>
       </c>
-      <c r="AG35">
+      <c r="AH35">
         <v>0.224387</v>
       </c>
-      <c r="AH35">
+      <c r="AI35">
         <v>0.71404800000000002</v>
       </c>
-      <c r="AJ35" t="s">
+      <c r="AK35" t="s">
         <v>63</v>
       </c>
-      <c r="AK35" t="s">
+      <c r="AL35" t="s">
         <v>29</v>
       </c>
-      <c r="AL35">
+      <c r="AM35">
         <f t="shared" si="6"/>
         <v>0.92841152560020834</v>
       </c>
-      <c r="AM35">
+      <c r="AN35">
         <f t="shared" si="7"/>
         <v>1.2747361887026691</v>
       </c>
-      <c r="AN35">
+      <c r="AO35">
         <f t="shared" si="8"/>
         <v>1.6602751246470837</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:41">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -44456,74 +44489,74 @@
       <c r="M36">
         <v>0.24564</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>99409</v>
       </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
         <v>30</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <v>45.440199999999997</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>44.572400000000002</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>99.113500000000002</v>
       </c>
-      <c r="V36" t="s">
+      <c r="W36" t="s">
         <v>63</v>
       </c>
-      <c r="W36" t="s">
+      <c r="X36" t="s">
         <v>30</v>
       </c>
-      <c r="X36">
+      <c r="Y36">
         <v>10.210000000000001</v>
       </c>
-      <c r="Y36">
+      <c r="Z36">
         <v>6.12</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>6.53</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>7.35</v>
       </c>
-      <c r="AD36" t="s">
+      <c r="AE36" t="s">
         <v>63</v>
       </c>
-      <c r="AE36" t="s">
+      <c r="AF36" t="s">
         <v>30</v>
       </c>
-      <c r="AF36">
+      <c r="AG36">
         <v>0.47320299999999998</v>
       </c>
-      <c r="AG36">
+      <c r="AH36">
         <v>0.24828700000000001</v>
       </c>
-      <c r="AH36">
+      <c r="AI36">
         <v>0.80028500000000002</v>
       </c>
-      <c r="AJ36" t="s">
+      <c r="AK36" t="s">
         <v>63</v>
       </c>
-      <c r="AK36" t="s">
+      <c r="AL36" t="s">
         <v>30</v>
       </c>
-      <c r="AL36">
+      <c r="AM36">
         <f t="shared" si="6"/>
         <v>0.9142069631522296</v>
       </c>
-      <c r="AM36">
+      <c r="AN36">
         <f t="shared" si="7"/>
         <v>0.89674777937611283</v>
       </c>
-      <c r="AN36">
+      <c r="AO36">
         <f t="shared" si="8"/>
         <v>1.9940548642477038</v>
       </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:41">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -44557,74 +44590,74 @@
       <c r="M37">
         <v>0.27635999999999999</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>96376</v>
       </c>
-      <c r="R37" t="s">
+      <c r="S37" t="s">
         <v>31</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <v>46.103700000000003</v>
       </c>
-      <c r="T37">
+      <c r="U37">
         <v>47.601999999999997</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>51.347200000000001</v>
       </c>
-      <c r="V37" t="s">
+      <c r="W37" t="s">
         <v>63</v>
       </c>
-      <c r="W37" t="s">
+      <c r="X37" t="s">
         <v>31</v>
       </c>
-      <c r="X37">
+      <c r="Y37">
         <v>9.81</v>
       </c>
-      <c r="Y37">
+      <c r="Z37">
         <v>5.59</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>6.07</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>4.7699999999999996</v>
       </c>
-      <c r="AD37" t="s">
+      <c r="AE37" t="s">
         <v>63</v>
       </c>
-      <c r="AE37" t="s">
+      <c r="AF37" t="s">
         <v>31</v>
       </c>
-      <c r="AF37">
+      <c r="AG37">
         <v>0.28071499999999999</v>
       </c>
-      <c r="AG37">
+      <c r="AH37">
         <v>0.22880700000000001</v>
       </c>
-      <c r="AH37">
+      <c r="AI37">
         <v>0.62939699999999998</v>
       </c>
-      <c r="AJ37" t="s">
+      <c r="AK37" t="s">
         <v>63</v>
       </c>
-      <c r="AK37" t="s">
+      <c r="AL37" t="s">
         <v>31</v>
       </c>
-      <c r="AL37">
+      <c r="AM37">
         <f t="shared" si="6"/>
         <v>0.95674649290279745</v>
       </c>
-      <c r="AM37">
+      <c r="AN37">
         <f t="shared" si="7"/>
         <v>0.98783929609031296</v>
       </c>
-      <c r="AN37">
+      <c r="AO37">
         <f t="shared" si="8"/>
         <v>1.0655598904291526</v>
       </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:41">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -44658,74 +44691,74 @@
       <c r="M38">
         <v>0.23613000000000001</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>98555</v>
       </c>
-      <c r="R38" t="s">
+      <c r="S38" t="s">
         <v>32</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <v>44.6051</v>
       </c>
-      <c r="T38">
+      <c r="U38">
         <v>48.090800000000002</v>
       </c>
-      <c r="U38">
+      <c r="V38">
         <v>83.8523</v>
       </c>
-      <c r="V38" t="s">
+      <c r="W38" t="s">
         <v>63</v>
       </c>
-      <c r="W38" t="s">
+      <c r="X38" t="s">
         <v>32</v>
       </c>
-      <c r="X38">
+      <c r="Y38">
         <v>11.78</v>
       </c>
-      <c r="Y38">
+      <c r="Z38">
         <v>4.75</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>5.75</v>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <v>7.44</v>
       </c>
-      <c r="AD38" t="s">
+      <c r="AE38" t="s">
         <v>63</v>
       </c>
-      <c r="AE38" t="s">
+      <c r="AF38" t="s">
         <v>32</v>
       </c>
-      <c r="AF38">
+      <c r="AG38">
         <v>0.28042800000000001</v>
       </c>
-      <c r="AG38">
+      <c r="AH38">
         <v>0.235206</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>0.71379099999999995</v>
       </c>
-      <c r="AJ38" t="s">
+      <c r="AK38" t="s">
         <v>63</v>
       </c>
-      <c r="AK38" t="s">
+      <c r="AL38" t="s">
         <v>32</v>
       </c>
-      <c r="AL38">
+      <c r="AM38">
         <f t="shared" si="6"/>
         <v>0.90518187813911011</v>
       </c>
-      <c r="AM38">
+      <c r="AN38">
         <f t="shared" si="7"/>
         <v>0.97591801532139422</v>
       </c>
-      <c r="AN38">
+      <c r="AO38">
         <f t="shared" si="8"/>
         <v>1.7016346202627974</v>
       </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:41">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -44759,74 +44792,74 @@
       <c r="M39">
         <v>0.28089999999999998</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>92932</v>
       </c>
-      <c r="R39" t="s">
+      <c r="S39" t="s">
         <v>33</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <v>42.772599999999997</v>
       </c>
-      <c r="T39">
+      <c r="U39">
         <v>44.548499999999997</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>43.503500000000003</v>
       </c>
-      <c r="V39" t="s">
+      <c r="W39" t="s">
         <v>63</v>
       </c>
-      <c r="W39" t="s">
+      <c r="X39" t="s">
         <v>33</v>
       </c>
-      <c r="X39">
+      <c r="Y39">
         <v>12</v>
       </c>
-      <c r="Y39">
+      <c r="Z39">
         <v>6.24</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>6.04</v>
       </c>
-      <c r="AA39">
+      <c r="AB39">
         <v>4.18</v>
       </c>
-      <c r="AD39" t="s">
+      <c r="AE39" t="s">
         <v>63</v>
       </c>
-      <c r="AE39" t="s">
+      <c r="AF39" t="s">
         <v>33</v>
       </c>
-      <c r="AF39">
+      <c r="AG39">
         <v>0.27169199999999999</v>
       </c>
-      <c r="AG39">
+      <c r="AH39">
         <v>0.227655</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>0.63714400000000004</v>
       </c>
-      <c r="AJ39" t="s">
+      <c r="AK39" t="s">
         <v>63</v>
       </c>
-      <c r="AK39" t="s">
+      <c r="AL39" t="s">
         <v>33</v>
       </c>
-      <c r="AL39">
+      <c r="AM39">
         <f t="shared" si="6"/>
         <v>0.92051392415960054</v>
       </c>
-      <c r="AM39">
+      <c r="AN39">
         <f t="shared" si="7"/>
         <v>0.95873326733525588</v>
       </c>
-      <c r="AN39">
+      <c r="AO39">
         <f t="shared" si="8"/>
         <v>0.93624370507467825</v>
       </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:41">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -44860,74 +44893,74 @@
       <c r="M40">
         <v>0.21942</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>92765</v>
       </c>
-      <c r="R40" t="s">
+      <c r="S40" t="s">
         <v>34</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <v>41.648400000000002</v>
       </c>
-      <c r="T40">
+      <c r="U40">
         <v>41.2134</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>43.114100000000001</v>
       </c>
-      <c r="V40" t="s">
+      <c r="W40" t="s">
         <v>63</v>
       </c>
-      <c r="W40" t="s">
+      <c r="X40" t="s">
         <v>34</v>
       </c>
-      <c r="X40">
+      <c r="Y40">
         <v>13.26</v>
       </c>
-      <c r="Y40">
+      <c r="Z40">
         <v>4.78</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>3.15</v>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <v>4.8</v>
       </c>
-      <c r="AD40" t="s">
+      <c r="AE40" t="s">
         <v>63</v>
       </c>
-      <c r="AE40" t="s">
+      <c r="AF40" t="s">
         <v>34</v>
       </c>
-      <c r="AF40">
+      <c r="AG40">
         <v>0.25173400000000001</v>
       </c>
-      <c r="AG40">
+      <c r="AH40">
         <v>0.213057</v>
       </c>
-      <c r="AH40">
+      <c r="AI40">
         <v>0.66978000000000004</v>
       </c>
-      <c r="AJ40" t="s">
+      <c r="AK40" t="s">
         <v>63</v>
       </c>
-      <c r="AK40" t="s">
+      <c r="AL40" t="s">
         <v>34</v>
       </c>
-      <c r="AL40">
+      <c r="AM40">
         <f t="shared" si="6"/>
         <v>0.89793348784563143</v>
       </c>
-      <c r="AM40">
+      <c r="AN40">
         <f t="shared" si="7"/>
         <v>0.88855495068183044</v>
       </c>
-      <c r="AN40">
+      <c r="AO40">
         <f t="shared" si="8"/>
         <v>0.92953376812375355</v>
       </c>
     </row>
-    <row r="41" spans="1:40">
+    <row r="41" spans="1:41">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -44961,74 +44994,74 @@
       <c r="M41">
         <v>0.23715</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>93324</v>
       </c>
-      <c r="R41" t="s">
+      <c r="S41" t="s">
         <v>35</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <v>38.800899999999999</v>
       </c>
-      <c r="T41">
+      <c r="U41">
         <v>47.312199999999997</v>
       </c>
-      <c r="U41">
+      <c r="V41">
         <v>47.7607</v>
       </c>
-      <c r="V41" t="s">
+      <c r="W41" t="s">
         <v>63</v>
       </c>
-      <c r="W41" t="s">
+      <c r="X41" t="s">
         <v>35</v>
       </c>
-      <c r="X41">
+      <c r="Y41">
         <v>10.199999999999999</v>
       </c>
-      <c r="Y41">
+      <c r="Z41">
         <v>6.56</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AA41">
+      <c r="AB41">
         <v>5.15</v>
       </c>
-      <c r="AD41" t="s">
+      <c r="AE41" t="s">
         <v>63</v>
       </c>
-      <c r="AE41" t="s">
+      <c r="AF41" t="s">
         <v>35</v>
       </c>
-      <c r="AF41">
+      <c r="AG41">
         <v>0.29743799999999998</v>
       </c>
-      <c r="AG41">
+      <c r="AH41">
         <v>0.230603</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>0.65063700000000002</v>
       </c>
-      <c r="AJ41" t="s">
+      <c r="AK41" t="s">
         <v>63</v>
       </c>
-      <c r="AK41" t="s">
+      <c r="AL41" t="s">
         <v>35</v>
       </c>
-      <c r="AL41">
+      <c r="AM41">
         <f t="shared" si="6"/>
         <v>0.83153101024388154</v>
       </c>
-      <c r="AM41">
+      <c r="AN41">
         <f t="shared" si="7"/>
         <v>1.0139342505679139</v>
       </c>
-      <c r="AN41">
+      <c r="AO41">
         <f t="shared" si="8"/>
         <v>1.0235459260211734</v>
       </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:41">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -45062,74 +45095,74 @@
       <c r="M42">
         <v>0.20049</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>99782</v>
       </c>
-      <c r="R42" t="s">
+      <c r="S42" t="s">
         <v>36</v>
       </c>
-      <c r="S42">
+      <c r="T42">
         <v>43.7027</v>
       </c>
-      <c r="T42">
+      <c r="U42">
         <v>46.207299999999996</v>
       </c>
-      <c r="U42">
+      <c r="V42">
         <v>84.319900000000004</v>
       </c>
-      <c r="V42" t="s">
+      <c r="W42" t="s">
         <v>63</v>
       </c>
-      <c r="W42" t="s">
+      <c r="X42" t="s">
         <v>36</v>
       </c>
-      <c r="X42">
+      <c r="Y42">
         <v>13.35</v>
       </c>
-      <c r="Y42">
+      <c r="Z42">
         <v>6.33</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>6.39</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <v>7.84</v>
       </c>
-      <c r="AD42" t="s">
+      <c r="AE42" t="s">
         <v>63</v>
       </c>
-      <c r="AE42" t="s">
+      <c r="AF42" t="s">
         <v>36</v>
       </c>
-      <c r="AF42">
+      <c r="AG42">
         <v>0.39188899999999999</v>
       </c>
-      <c r="AG42">
+      <c r="AH42">
         <v>0.22411800000000001</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>0.77076699999999998</v>
       </c>
-      <c r="AJ42" t="s">
+      <c r="AK42" t="s">
         <v>63</v>
       </c>
-      <c r="AK42" t="s">
+      <c r="AL42" t="s">
         <v>36</v>
       </c>
-      <c r="AL42">
+      <c r="AM42">
         <f t="shared" si="6"/>
         <v>0.8759636006494157</v>
       </c>
-      <c r="AM42">
+      <c r="AN42">
         <f t="shared" si="7"/>
         <v>0.92616503978673503</v>
       </c>
-      <c r="AN42">
+      <c r="AO42">
         <f t="shared" si="8"/>
         <v>1.6900823795875008</v>
       </c>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:41">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -45163,117 +45196,117 @@
       <c r="M43">
         <v>0.21032999999999999</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>100000</v>
       </c>
-      <c r="R43" t="s">
+      <c r="S43" t="s">
         <v>37</v>
       </c>
-      <c r="S43">
+      <c r="T43">
         <v>47.305599999999998</v>
       </c>
-      <c r="T43">
+      <c r="U43">
         <v>47.401299999999999</v>
       </c>
-      <c r="U43">
+      <c r="V43">
         <v>46.840200000000003</v>
       </c>
-      <c r="V43" t="s">
+      <c r="W43" t="s">
         <v>63</v>
       </c>
-      <c r="W43" t="s">
+      <c r="X43" t="s">
         <v>37</v>
       </c>
-      <c r="X43">
+      <c r="Y43">
         <v>10.47</v>
       </c>
-      <c r="Y43">
+      <c r="Z43">
         <v>8.06</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>6.46</v>
       </c>
-      <c r="AA43">
+      <c r="AB43">
         <v>11.51</v>
       </c>
-      <c r="AD43" t="s">
+      <c r="AE43" t="s">
         <v>63</v>
       </c>
-      <c r="AE43" t="s">
+      <c r="AF43" t="s">
         <v>37</v>
       </c>
-      <c r="AF43">
+      <c r="AG43">
         <v>0.37688500000000003</v>
       </c>
-      <c r="AG43">
+      <c r="AH43">
         <v>0.25006699999999998</v>
       </c>
-      <c r="AH43">
+      <c r="AI43">
         <v>0.73384899999999997</v>
       </c>
-      <c r="AJ43" t="s">
+      <c r="AK43" t="s">
         <v>63</v>
       </c>
-      <c r="AK43" t="s">
+      <c r="AL43" t="s">
         <v>37</v>
       </c>
-      <c r="AL43">
+      <c r="AM43">
         <f t="shared" si="6"/>
         <v>0.94611199999999995</v>
       </c>
-      <c r="AM43">
+      <c r="AN43">
         <f t="shared" si="7"/>
         <v>0.94802599999999992</v>
       </c>
-      <c r="AN43">
+      <c r="AO43">
         <f t="shared" si="8"/>
         <v>0.93680400000000008</v>
       </c>
     </row>
-    <row r="44" spans="1:40">
-      <c r="Q44" t="s">
+    <row r="44" spans="1:41">
+      <c r="R44" t="s">
         <v>63</v>
       </c>
-      <c r="V44" t="s">
+      <c r="W44" t="s">
         <v>63</v>
       </c>
-      <c r="AD44" t="s">
+      <c r="AE44" t="s">
         <v>63</v>
       </c>
-      <c r="AJ44" t="s">
+      <c r="AK44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:41">
       <c r="A45" t="s">
         <v>40</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>63</v>
       </c>
-      <c r="R45" t="s">
+      <c r="S45" t="s">
         <v>40</v>
       </c>
-      <c r="V45" t="s">
+      <c r="W45" t="s">
         <v>63</v>
       </c>
-      <c r="W45" t="s">
+      <c r="X45" t="s">
         <v>54</v>
       </c>
-      <c r="AD45" t="s">
+      <c r="AE45" t="s">
         <v>63</v>
       </c>
-      <c r="AE45" t="s">
+      <c r="AF45" t="s">
         <v>56</v>
       </c>
-      <c r="AJ45" t="s">
+      <c r="AK45" t="s">
         <v>63</v>
       </c>
-      <c r="AK45" t="s">
+      <c r="AL45" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:41">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -45319,80 +45352,80 @@
       <c r="O46">
         <v>110.47</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>99833</v>
       </c>
-      <c r="R46" t="s">
+      <c r="S46" t="s">
         <v>26</v>
       </c>
-      <c r="S46">
+      <c r="T46">
         <v>1.1568700000000001</v>
       </c>
-      <c r="T46">
+      <c r="U46">
         <v>0.80389999999999995</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>0.55035000000000001</v>
       </c>
-      <c r="V46" t="s">
+      <c r="W46" t="s">
         <v>63</v>
       </c>
-      <c r="W46" t="s">
+      <c r="X46" t="s">
         <v>26</v>
       </c>
-      <c r="X46">
+      <c r="Y46">
         <v>0.96</v>
       </c>
-      <c r="Y46">
+      <c r="Z46">
         <v>1.4</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>0.02</v>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <v>0.01</v>
       </c>
-      <c r="AB46">
+      <c r="AC46">
         <v>1.43</v>
       </c>
-      <c r="AC46">
+      <c r="AD46">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AD46" t="s">
+      <c r="AE46" t="s">
         <v>63</v>
       </c>
-      <c r="AE46" t="s">
+      <c r="AF46" t="s">
         <v>26</v>
       </c>
-      <c r="AF46">
+      <c r="AG46">
         <v>0.21</v>
       </c>
-      <c r="AG46">
+      <c r="AH46">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="AH46">
+      <c r="AI46">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="AI46">
+      <c r="AJ46">
         <v>0.26600000000000001</v>
       </c>
-      <c r="AJ46" t="s">
+      <c r="AK46" t="s">
         <v>63</v>
       </c>
-      <c r="AK46" t="s">
+      <c r="AL46" t="s">
         <v>26</v>
       </c>
-      <c r="AL46">
+      <c r="AM46">
         <v>1.1568700000000001</v>
       </c>
-      <c r="AM46">
+      <c r="AN46">
         <v>0.80389999999999995</v>
       </c>
-      <c r="AN46">
+      <c r="AO46">
         <v>0.55035000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:40">
+    <row r="47" spans="1:41">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -45438,80 +45471,80 @@
       <c r="O47">
         <v>230.39</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>89229</v>
       </c>
-      <c r="R47" t="s">
+      <c r="S47" t="s">
         <v>27</v>
       </c>
-      <c r="S47">
+      <c r="T47">
         <v>1.19113</v>
       </c>
-      <c r="T47">
+      <c r="U47">
         <v>0.1527</v>
       </c>
-      <c r="U47">
+      <c r="V47">
         <v>0.37875999999999999</v>
       </c>
-      <c r="V47" t="s">
+      <c r="W47" t="s">
         <v>63</v>
       </c>
-      <c r="W47" t="s">
+      <c r="X47" t="s">
         <v>27</v>
       </c>
-      <c r="X47">
+      <c r="Y47">
         <v>3.48</v>
       </c>
-      <c r="Y47">
+      <c r="Z47">
         <v>6.48</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>0.02</v>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <v>0.03</v>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <v>13.24</v>
       </c>
-      <c r="AC47">
+      <c r="AD47">
         <v>21.27</v>
       </c>
-      <c r="AD47" t="s">
+      <c r="AE47" t="s">
         <v>63</v>
       </c>
-      <c r="AE47" t="s">
+      <c r="AF47" t="s">
         <v>27</v>
       </c>
-      <c r="AF47">
+      <c r="AG47">
         <v>0.192</v>
       </c>
-      <c r="AG47">
+      <c r="AH47">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="AH47">
+      <c r="AI47">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="AI47">
+      <c r="AJ47">
         <v>0.378</v>
       </c>
-      <c r="AJ47" t="s">
+      <c r="AK47" t="s">
         <v>63</v>
       </c>
-      <c r="AK47" t="s">
+      <c r="AL47" t="s">
         <v>27</v>
       </c>
-      <c r="AL47">
+      <c r="AM47">
         <v>1.19113</v>
       </c>
-      <c r="AM47">
+      <c r="AN47">
         <v>0.1527</v>
       </c>
-      <c r="AN47">
+      <c r="AO47">
         <v>0.37875999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:41">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -45557,80 +45590,80 @@
       <c r="O48">
         <v>66.27</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>99859</v>
       </c>
-      <c r="R48" t="s">
+      <c r="S48" t="s">
         <v>28</v>
       </c>
-      <c r="S48">
+      <c r="T48">
         <v>1.22088</v>
       </c>
-      <c r="T48">
+      <c r="U48">
         <v>8.1089999999999995E-2</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <v>0.52871000000000001</v>
       </c>
-      <c r="V48" t="s">
+      <c r="W48" t="s">
         <v>63</v>
       </c>
-      <c r="W48" t="s">
+      <c r="X48" t="s">
         <v>28</v>
       </c>
-      <c r="X48">
+      <c r="Y48">
         <v>2.09</v>
       </c>
-      <c r="Y48">
+      <c r="Z48">
         <v>4.03</v>
-      </c>
-      <c r="Z48">
-        <v>0.02</v>
       </c>
       <c r="AA48">
         <v>0.02</v>
       </c>
       <c r="AB48">
+        <v>0.02</v>
+      </c>
+      <c r="AC48">
         <v>2.04</v>
       </c>
-      <c r="AC48">
+      <c r="AD48">
         <v>5.12</v>
       </c>
-      <c r="AD48" t="s">
+      <c r="AE48" t="s">
         <v>63</v>
       </c>
-      <c r="AE48" t="s">
+      <c r="AF48" t="s">
         <v>28</v>
       </c>
-      <c r="AF48">
+      <c r="AG48">
         <v>0.189</v>
       </c>
-      <c r="AG48">
+      <c r="AH48">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="AH48">
+      <c r="AI48">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="AI48">
+      <c r="AJ48">
         <v>0.17799999999999999</v>
       </c>
-      <c r="AJ48" t="s">
+      <c r="AK48" t="s">
         <v>63</v>
       </c>
-      <c r="AK48" t="s">
+      <c r="AL48" t="s">
         <v>28</v>
       </c>
-      <c r="AL48">
+      <c r="AM48">
         <v>1.22088</v>
       </c>
-      <c r="AM48">
+      <c r="AN48">
         <v>8.1089999999999995E-2</v>
       </c>
-      <c r="AN48">
+      <c r="AO48">
         <v>0.52871000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:41">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -45676,80 +45709,80 @@
       <c r="O49">
         <v>93.41</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>99882</v>
       </c>
-      <c r="R49" t="s">
+      <c r="S49" t="s">
         <v>29</v>
       </c>
-      <c r="S49">
+      <c r="T49">
         <v>1.3065599999999999</v>
       </c>
-      <c r="T49">
+      <c r="U49">
         <v>9.4549999999999995E-2</v>
       </c>
-      <c r="U49">
+      <c r="V49">
         <v>0.41597000000000001</v>
       </c>
-      <c r="V49" t="s">
+      <c r="W49" t="s">
         <v>63</v>
       </c>
-      <c r="W49" t="s">
+      <c r="X49" t="s">
         <v>29</v>
       </c>
-      <c r="X49">
+      <c r="Y49">
         <v>2.89</v>
       </c>
-      <c r="Y49">
+      <c r="Z49">
         <v>5.25</v>
-      </c>
-      <c r="Z49">
-        <v>0.02</v>
       </c>
       <c r="AA49">
         <v>0.02</v>
       </c>
       <c r="AB49">
+        <v>0.02</v>
+      </c>
+      <c r="AC49">
         <v>2.93</v>
       </c>
-      <c r="AC49">
+      <c r="AD49">
         <v>6.07</v>
       </c>
-      <c r="AD49" t="s">
+      <c r="AE49" t="s">
         <v>63</v>
       </c>
-      <c r="AE49" t="s">
+      <c r="AF49" t="s">
         <v>29</v>
       </c>
-      <c r="AF49">
+      <c r="AG49">
         <v>0.183</v>
       </c>
-      <c r="AG49">
+      <c r="AH49">
         <v>0.05</v>
       </c>
-      <c r="AH49">
+      <c r="AI49">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="AI49">
+      <c r="AJ49">
         <v>0.189</v>
       </c>
-      <c r="AJ49" t="s">
+      <c r="AK49" t="s">
         <v>63</v>
       </c>
-      <c r="AK49" t="s">
+      <c r="AL49" t="s">
         <v>29</v>
       </c>
-      <c r="AL49">
+      <c r="AM49">
         <v>1.3065599999999999</v>
       </c>
-      <c r="AM49">
+      <c r="AN49">
         <v>9.4549999999999995E-2</v>
       </c>
-      <c r="AN49">
+      <c r="AO49">
         <v>0.41597000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:41">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -45795,80 +45828,80 @@
       <c r="O50">
         <v>184.25</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>99409</v>
       </c>
-      <c r="R50" t="s">
+      <c r="S50" t="s">
         <v>30</v>
       </c>
-      <c r="S50">
+      <c r="T50">
         <v>1.2458400000000001</v>
       </c>
-      <c r="T50">
+      <c r="U50">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="U50">
+      <c r="V50">
         <v>0.31872</v>
       </c>
-      <c r="V50" t="s">
+      <c r="W50" t="s">
         <v>63</v>
       </c>
-      <c r="W50" t="s">
+      <c r="X50" t="s">
         <v>30</v>
       </c>
-      <c r="X50">
+      <c r="Y50">
         <v>0.79</v>
       </c>
-      <c r="Y50">
+      <c r="Z50">
         <v>1.03</v>
       </c>
-      <c r="Z50">
+      <c r="AA50">
         <v>0.02</v>
       </c>
-      <c r="AA50">
+      <c r="AB50">
         <v>0.01</v>
       </c>
-      <c r="AB50">
+      <c r="AC50">
         <v>1.1399999999999999</v>
       </c>
-      <c r="AC50">
+      <c r="AD50">
         <v>1.45</v>
       </c>
-      <c r="AD50" t="s">
+      <c r="AE50" t="s">
         <v>63</v>
       </c>
-      <c r="AE50" t="s">
+      <c r="AF50" t="s">
         <v>30</v>
       </c>
-      <c r="AF50">
+      <c r="AG50">
         <v>0.217</v>
       </c>
-      <c r="AG50">
+      <c r="AH50">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="AH50">
+      <c r="AI50">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="AI50">
+      <c r="AJ50">
         <v>0.29599999999999999</v>
       </c>
-      <c r="AJ50" t="s">
+      <c r="AK50" t="s">
         <v>63</v>
       </c>
-      <c r="AK50" t="s">
+      <c r="AL50" t="s">
         <v>30</v>
       </c>
-      <c r="AL50">
+      <c r="AM50">
         <v>1.2458400000000001</v>
       </c>
-      <c r="AM50">
+      <c r="AN50">
         <v>7.8799999999999995E-2</v>
       </c>
-      <c r="AN50">
+      <c r="AO50">
         <v>0.31872</v>
       </c>
     </row>
-    <row r="51" spans="1:40">
+    <row r="51" spans="1:41">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -45914,80 +45947,80 @@
       <c r="O51">
         <v>209.71</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>96376</v>
       </c>
-      <c r="R51" t="s">
+      <c r="S51" t="s">
         <v>31</v>
       </c>
-      <c r="S51">
+      <c r="T51">
         <v>1.20699</v>
       </c>
-      <c r="T51">
+      <c r="U51">
         <v>8.4080000000000002E-2</v>
       </c>
-      <c r="U51">
+      <c r="V51">
         <v>0.28611999999999999</v>
       </c>
-      <c r="V51" t="s">
+      <c r="W51" t="s">
         <v>63</v>
       </c>
-      <c r="W51" t="s">
+      <c r="X51" t="s">
         <v>31</v>
       </c>
-      <c r="X51">
+      <c r="Y51">
         <v>0.8</v>
       </c>
-      <c r="Y51">
+      <c r="Z51">
         <v>3.58</v>
       </c>
-      <c r="Z51">
+      <c r="AA51">
         <v>0.02</v>
       </c>
-      <c r="AA51">
+      <c r="AB51">
         <v>0.04</v>
       </c>
-      <c r="AB51">
+      <c r="AC51">
         <v>1.18</v>
       </c>
-      <c r="AC51">
+      <c r="AD51">
         <v>7.87</v>
       </c>
-      <c r="AD51" t="s">
+      <c r="AE51" t="s">
         <v>63</v>
       </c>
-      <c r="AE51" t="s">
+      <c r="AF51" t="s">
         <v>31</v>
       </c>
-      <c r="AF51">
+      <c r="AG51">
         <v>0.17100000000000001</v>
       </c>
-      <c r="AG51">
+      <c r="AH51">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AH51">
+      <c r="AI51">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AI51">
+      <c r="AJ51">
         <v>0.46800000000000003</v>
       </c>
-      <c r="AJ51" t="s">
+      <c r="AK51" t="s">
         <v>63</v>
       </c>
-      <c r="AK51" t="s">
+      <c r="AL51" t="s">
         <v>31</v>
       </c>
-      <c r="AL51">
+      <c r="AM51">
         <v>1.20699</v>
       </c>
-      <c r="AM51">
+      <c r="AN51">
         <v>8.4080000000000002E-2</v>
       </c>
-      <c r="AN51">
+      <c r="AO51">
         <v>0.28611999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:40">
+    <row r="52" spans="1:41">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -46033,80 +46066,80 @@
       <c r="O52">
         <v>244.02</v>
       </c>
-      <c r="Q52">
+      <c r="R52">
         <v>98555</v>
       </c>
-      <c r="R52" t="s">
+      <c r="S52" t="s">
         <v>32</v>
       </c>
-      <c r="S52">
+      <c r="T52">
         <v>1.1654599999999999</v>
       </c>
-      <c r="T52">
+      <c r="U52">
         <v>7.8589999999999993E-2</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <v>0.22126000000000001</v>
       </c>
-      <c r="V52" t="s">
+      <c r="W52" t="s">
         <v>63</v>
       </c>
-      <c r="W52" t="s">
+      <c r="X52" t="s">
         <v>32</v>
       </c>
-      <c r="X52">
+      <c r="Y52">
         <v>0.49</v>
       </c>
-      <c r="Y52">
+      <c r="Z52">
         <v>0.89</v>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <v>0.01</v>
       </c>
-      <c r="AA52">
+      <c r="AB52">
         <v>0.02</v>
       </c>
-      <c r="AB52">
+      <c r="AC52">
         <v>1.37</v>
       </c>
-      <c r="AC52">
+      <c r="AD52">
         <v>2.97</v>
       </c>
-      <c r="AD52" t="s">
+      <c r="AE52" t="s">
         <v>63</v>
       </c>
-      <c r="AE52" t="s">
+      <c r="AF52" t="s">
         <v>32</v>
       </c>
-      <c r="AF52">
+      <c r="AG52">
         <v>0.16600000000000001</v>
       </c>
-      <c r="AG52">
+      <c r="AH52">
         <v>0.05</v>
       </c>
-      <c r="AH52">
+      <c r="AI52">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AI52">
+      <c r="AJ52">
         <v>0.184</v>
       </c>
-      <c r="AJ52" t="s">
+      <c r="AK52" t="s">
         <v>63</v>
       </c>
-      <c r="AK52" t="s">
+      <c r="AL52" t="s">
         <v>32</v>
       </c>
-      <c r="AL52">
+      <c r="AM52">
         <v>1.1654599999999999</v>
       </c>
-      <c r="AM52">
+      <c r="AN52">
         <v>7.8589999999999993E-2</v>
       </c>
-      <c r="AN52">
+      <c r="AO52">
         <v>0.22126000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:40">
+    <row r="53" spans="1:41">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -46152,80 +46185,80 @@
       <c r="O53">
         <v>380.21</v>
       </c>
-      <c r="Q53">
+      <c r="R53">
         <v>92932</v>
       </c>
-      <c r="R53" t="s">
+      <c r="S53" t="s">
         <v>33</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <v>1.17544</v>
       </c>
-      <c r="T53">
+      <c r="U53">
         <v>7.5850000000000001E-2</v>
       </c>
-      <c r="U53">
+      <c r="V53">
         <v>0.25051000000000001</v>
       </c>
-      <c r="V53" t="s">
+      <c r="W53" t="s">
         <v>63</v>
       </c>
-      <c r="W53" t="s">
+      <c r="X53" t="s">
         <v>33</v>
       </c>
-      <c r="X53">
+      <c r="Y53">
         <v>0.63</v>
       </c>
-      <c r="Y53">
+      <c r="Z53">
         <v>2.0099999999999998</v>
       </c>
-      <c r="Z53">
+      <c r="AA53">
         <v>0.02</v>
       </c>
-      <c r="AA53">
+      <c r="AB53">
         <v>0.03</v>
       </c>
-      <c r="AB53">
+      <c r="AC53">
         <v>0.88</v>
       </c>
-      <c r="AC53">
+      <c r="AD53">
         <v>4.2300000000000004</v>
       </c>
-      <c r="AD53" t="s">
+      <c r="AE53" t="s">
         <v>63</v>
       </c>
-      <c r="AE53" t="s">
+      <c r="AF53" t="s">
         <v>33</v>
       </c>
-      <c r="AF53">
+      <c r="AG53">
         <v>0.16</v>
       </c>
-      <c r="AG53">
+      <c r="AH53">
         <v>0.05</v>
       </c>
-      <c r="AH53">
+      <c r="AI53">
         <v>0.06</v>
       </c>
-      <c r="AI53">
+      <c r="AJ53">
         <v>0.46700000000000003</v>
       </c>
-      <c r="AJ53" t="s">
+      <c r="AK53" t="s">
         <v>63</v>
       </c>
-      <c r="AK53" t="s">
+      <c r="AL53" t="s">
         <v>33</v>
       </c>
-      <c r="AL53">
+      <c r="AM53">
         <v>1.17544</v>
       </c>
-      <c r="AM53">
+      <c r="AN53">
         <v>7.5850000000000001E-2</v>
       </c>
-      <c r="AN53">
+      <c r="AO53">
         <v>0.25051000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:40">
+    <row r="54" spans="1:41">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -46271,80 +46304,80 @@
       <c r="O54">
         <v>363.31</v>
       </c>
-      <c r="Q54">
+      <c r="R54">
         <v>92765</v>
       </c>
-      <c r="R54" t="s">
+      <c r="S54" t="s">
         <v>34</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>1.1959</v>
       </c>
-      <c r="T54">
+      <c r="U54">
         <v>7.1029999999999996E-2</v>
       </c>
-      <c r="U54">
+      <c r="V54">
         <v>0.22863</v>
       </c>
-      <c r="V54" t="s">
+      <c r="W54" t="s">
         <v>63</v>
       </c>
-      <c r="W54" t="s">
+      <c r="X54" t="s">
         <v>34</v>
       </c>
-      <c r="X54">
+      <c r="Y54">
         <v>0.45</v>
       </c>
-      <c r="Y54">
+      <c r="Z54">
         <v>3.97</v>
       </c>
-      <c r="Z54">
+      <c r="AA54">
         <v>0.02</v>
       </c>
-      <c r="AA54">
+      <c r="AB54">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AB54">
+      <c r="AC54">
         <v>1.75</v>
       </c>
-      <c r="AC54">
+      <c r="AD54">
         <v>35.909999999999997</v>
       </c>
-      <c r="AD54" t="s">
+      <c r="AE54" t="s">
         <v>63</v>
       </c>
-      <c r="AE54" t="s">
+      <c r="AF54" t="s">
         <v>34</v>
       </c>
-      <c r="AF54">
+      <c r="AG54">
         <v>0.154</v>
       </c>
-      <c r="AG54">
+      <c r="AH54">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="AH54">
+      <c r="AI54">
         <v>6.3E-2</v>
       </c>
-      <c r="AI54">
+      <c r="AJ54">
         <v>25</v>
       </c>
-      <c r="AJ54" t="s">
+      <c r="AK54" t="s">
         <v>63</v>
       </c>
-      <c r="AK54" t="s">
+      <c r="AL54" t="s">
         <v>34</v>
       </c>
-      <c r="AL54">
+      <c r="AM54">
         <v>1.1959</v>
       </c>
-      <c r="AM54">
+      <c r="AN54">
         <v>7.1029999999999996E-2</v>
       </c>
-      <c r="AN54">
+      <c r="AO54">
         <v>0.22863</v>
       </c>
     </row>
-    <row r="55" spans="1:40">
+    <row r="55" spans="1:41">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -46390,80 +46423,80 @@
       <c r="O55">
         <v>247.69</v>
       </c>
-      <c r="Q55">
+      <c r="R55">
         <v>93324</v>
       </c>
-      <c r="R55" t="s">
+      <c r="S55" t="s">
         <v>35</v>
       </c>
-      <c r="S55">
+      <c r="T55">
         <v>1.21194</v>
       </c>
-      <c r="T55">
+      <c r="U55">
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="U55">
+      <c r="V55">
         <v>0.33509</v>
       </c>
-      <c r="V55" t="s">
+      <c r="W55" t="s">
         <v>63</v>
       </c>
-      <c r="W55" t="s">
+      <c r="X55" t="s">
         <v>35</v>
       </c>
-      <c r="X55">
+      <c r="Y55">
         <v>0.92</v>
       </c>
-      <c r="Y55">
+      <c r="Z55">
         <v>2.2599999999999998</v>
       </c>
-      <c r="Z55">
+      <c r="AA55">
         <v>0.02</v>
       </c>
-      <c r="AA55">
+      <c r="AB55">
         <v>0.03</v>
       </c>
-      <c r="AB55">
+      <c r="AC55">
         <v>1.01</v>
       </c>
-      <c r="AC55">
+      <c r="AD55">
         <v>5.17</v>
       </c>
-      <c r="AD55" t="s">
+      <c r="AE55" t="s">
         <v>63</v>
       </c>
-      <c r="AE55" t="s">
+      <c r="AF55" t="s">
         <v>35</v>
       </c>
-      <c r="AF55">
+      <c r="AG55">
         <v>0.16900000000000001</v>
       </c>
-      <c r="AG55">
+      <c r="AH55">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AH55">
+      <c r="AI55">
         <v>6.2E-2</v>
       </c>
-      <c r="AI55">
+      <c r="AJ55">
         <v>0.45100000000000001</v>
       </c>
-      <c r="AJ55" t="s">
+      <c r="AK55" t="s">
         <v>63</v>
       </c>
-      <c r="AK55" t="s">
+      <c r="AL55" t="s">
         <v>35</v>
       </c>
-      <c r="AL55">
+      <c r="AM55">
         <v>1.21194</v>
       </c>
-      <c r="AM55">
+      <c r="AN55">
         <v>7.7499999999999999E-2</v>
       </c>
-      <c r="AN55">
+      <c r="AO55">
         <v>0.33509</v>
       </c>
     </row>
-    <row r="56" spans="1:40">
+    <row r="56" spans="1:41">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -46509,80 +46542,80 @@
       <c r="O56">
         <v>684.52</v>
       </c>
-      <c r="Q56">
+      <c r="R56">
         <v>99782</v>
       </c>
-      <c r="R56" t="s">
+      <c r="S56" t="s">
         <v>36</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <v>1.16275</v>
       </c>
-      <c r="T56">
+      <c r="U56">
         <v>7.8030000000000002E-2</v>
       </c>
-      <c r="U56">
+      <c r="V56">
         <v>0.43812000000000001</v>
       </c>
-      <c r="V56" t="s">
+      <c r="W56" t="s">
         <v>63</v>
       </c>
-      <c r="W56" t="s">
+      <c r="X56" t="s">
         <v>36</v>
       </c>
-      <c r="X56">
+      <c r="Y56">
         <v>2.16</v>
       </c>
-      <c r="Y56">
+      <c r="Z56">
         <v>2.95</v>
-      </c>
-      <c r="Z56">
-        <v>0.02</v>
       </c>
       <c r="AA56">
         <v>0.02</v>
       </c>
       <c r="AB56">
+        <v>0.02</v>
+      </c>
+      <c r="AC56">
         <v>5.26</v>
       </c>
-      <c r="AC56">
+      <c r="AD56">
         <v>6.86</v>
       </c>
-      <c r="AD56" t="s">
+      <c r="AE56" t="s">
         <v>63</v>
       </c>
-      <c r="AE56" t="s">
+      <c r="AF56" t="s">
         <v>36</v>
       </c>
-      <c r="AF56">
+      <c r="AG56">
         <v>0.184</v>
       </c>
-      <c r="AG56">
+      <c r="AH56">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="AH56">
+      <c r="AI56">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="AI56">
+      <c r="AJ56">
         <v>0.17599999999999999</v>
       </c>
-      <c r="AJ56" t="s">
+      <c r="AK56" t="s">
         <v>63</v>
       </c>
-      <c r="AK56" t="s">
+      <c r="AL56" t="s">
         <v>36</v>
       </c>
-      <c r="AL56">
+      <c r="AM56">
         <v>1.16275</v>
       </c>
-      <c r="AM56">
+      <c r="AN56">
         <v>7.8030000000000002E-2</v>
       </c>
-      <c r="AN56">
+      <c r="AO56">
         <v>0.43812000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:40">
+    <row r="57" spans="1:41">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -46628,76 +46661,76 @@
       <c r="O57">
         <v>145.94</v>
       </c>
-      <c r="Q57">
+      <c r="R57">
         <v>100000</v>
       </c>
-      <c r="R57" t="s">
+      <c r="S57" t="s">
         <v>37</v>
       </c>
-      <c r="S57">
+      <c r="T57">
         <v>1.1581999999999999</v>
       </c>
-      <c r="T57">
+      <c r="U57">
         <v>7.7280000000000001E-2</v>
       </c>
-      <c r="U57">
+      <c r="V57">
         <v>0.26918999999999998</v>
       </c>
-      <c r="V57" t="s">
+      <c r="W57" t="s">
         <v>63</v>
       </c>
-      <c r="W57" t="s">
+      <c r="X57" t="s">
         <v>37</v>
       </c>
-      <c r="X57">
+      <c r="Y57">
         <v>0.31</v>
       </c>
-      <c r="Y57">
+      <c r="Z57">
         <v>0.32</v>
       </c>
-      <c r="Z57">
+      <c r="AA57">
         <v>0.02</v>
       </c>
-      <c r="AA57">
+      <c r="AB57">
         <v>0.01</v>
       </c>
-      <c r="AB57">
+      <c r="AC57">
         <v>0.71</v>
       </c>
-      <c r="AC57">
+      <c r="AD57">
         <v>0.8</v>
       </c>
-      <c r="AD57" t="s">
+      <c r="AE57" t="s">
         <v>63</v>
       </c>
-      <c r="AE57" t="s">
+      <c r="AF57" t="s">
         <v>37</v>
       </c>
-      <c r="AF57">
+      <c r="AG57">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AG57">
+      <c r="AH57">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="AH57">
+      <c r="AI57">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AI57">
+      <c r="AJ57">
         <v>0.20100000000000001</v>
       </c>
-      <c r="AJ57" t="s">
+      <c r="AK57" t="s">
         <v>63</v>
       </c>
-      <c r="AK57" t="s">
+      <c r="AL57" t="s">
         <v>37</v>
       </c>
-      <c r="AL57">
+      <c r="AM57">
         <v>1.1581999999999999</v>
       </c>
-      <c r="AM57">
+      <c r="AN57">
         <v>7.7280000000000001E-2</v>
       </c>
-      <c r="AN57">
+      <c r="AO57">
         <v>0.26918999999999998</v>
       </c>
     </row>
